--- a/29-employee-testing-service/question_bank_pool_001.xlsx
+++ b/29-employee-testing-service/question_bank_pool_001.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Вопросы'!$A$1:$M$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Варианты'!$A$1:$F$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Назначение_по_должности'!$A$1:$D$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Программы'!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Программы'!$A$1:$L$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Источники'!$A$1:$F$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Справочники'!$A$1:$E$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Инструкция'!$A$1:$B$7</definedName>
@@ -195,7 +195,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Таблица3" displayName="Таблица3" ref="A1:D2" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Таблица3" displayName="Таблица3" ref="A1:D205" headerRowCount="1">
   <autoFilter ref="A1:D2"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Код вопроса"/>
@@ -208,20 +208,21 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="A1:K2" headerRowCount="1">
-  <autoFilter ref="A1:K2"/>
-  <tableColumns count="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица4" displayName="Таблица4" ref="A1:L2" headerRowCount="1">
+  <autoFilter ref="A1:L2"/>
+  <tableColumns count="12">
     <tableColumn id="1" name="Код программы"/>
     <tableColumn id="2" name="Название"/>
-    <tableColumn id="3" name="Официальная должность"/>
+    <tableColumn id="3" name="Официальные должности"/>
     <tableColumn id="4" name="Темы"/>
     <tableColumn id="5" name="Число вопросов"/>
     <tableColumn id="6" name="Время, минут"/>
     <tableColumn id="7" name="Порог, %"/>
     <tableColumn id="8" name="Попыток"/>
-    <tableColumn id="9" name="Срок результата, месяцев"/>
-    <tableColumn id="10" name="Статус"/>
-    <tableColumn id="11" name="Версия"/>
+    <tableColumn id="9" name="Период попыток"/>
+    <tableColumn id="10" name="Срок действия результата"/>
+    <tableColumn id="11" name="Статус"/>
+    <tableColumn id="12" name="Версия"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1"/>
 </table>
@@ -268,8 +269,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="ОтчетПула001" displayName="ОтчетПула001" ref="A1:B26" headerRowCount="1">
-  <autoFilter ref="A1:B26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="ОтчетПула001" displayName="ОтчетПула001" ref="A1:B30" headerRowCount="1">
+  <autoFilter ref="A1:B30"/>
   <tableColumns count="2">
     <tableColumn id="1" name="Показатель"/>
     <tableColumn id="2" name="Значение"/>
@@ -705,12 +706,12 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M2" s="3" t="n"/>
@@ -768,12 +769,12 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M3" s="3" t="n"/>
@@ -831,12 +832,12 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M4" s="3" t="n"/>
@@ -894,12 +895,12 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M5" s="3" t="n"/>
@@ -957,12 +958,12 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M6" s="3" t="n"/>
@@ -1020,12 +1021,12 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M7" s="3" t="n"/>
@@ -1083,12 +1084,12 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M8" s="3" t="n"/>
@@ -1146,12 +1147,12 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M9" s="3" t="n"/>
@@ -1209,12 +1210,12 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M10" s="3" t="n"/>
@@ -1272,12 +1273,12 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M11" s="3" t="n"/>
@@ -1335,12 +1336,12 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M12" s="3" t="n"/>
@@ -1398,12 +1399,12 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M13" s="3" t="n"/>
@@ -1461,12 +1462,12 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M14" s="3" t="n"/>
@@ -1524,12 +1525,12 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M15" s="3" t="n"/>
@@ -1587,12 +1588,12 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M16" s="3" t="n"/>
@@ -1650,12 +1651,12 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M17" s="3" t="n"/>
@@ -1713,12 +1714,12 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M18" s="3" t="n"/>
@@ -1776,12 +1777,12 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M19" s="3" t="n"/>
@@ -1839,12 +1840,12 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M20" s="3" t="n"/>
@@ -1902,12 +1903,12 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M21" s="3" t="n"/>
@@ -1965,12 +1966,12 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M22" s="3" t="n"/>
@@ -2028,12 +2029,12 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M23" s="3" t="n"/>
@@ -2091,12 +2092,12 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M24" s="3" t="n"/>
@@ -2154,12 +2155,12 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M25" s="3" t="n"/>
@@ -2217,12 +2218,12 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M26" s="3" t="n"/>
@@ -2280,12 +2281,12 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M27" s="3" t="n"/>
@@ -2343,12 +2344,12 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M28" s="3" t="n"/>
@@ -2406,12 +2407,12 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M29" s="3" t="n"/>
@@ -2469,12 +2470,12 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M30" s="3" t="n"/>
@@ -2532,12 +2533,12 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M31" s="3" t="n"/>
@@ -2595,12 +2596,12 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M32" s="3" t="n"/>
@@ -2658,12 +2659,12 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M33" s="3" t="n"/>
@@ -2721,12 +2722,12 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M34" s="3" t="n"/>
@@ -2784,12 +2785,12 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M35" s="3" t="n"/>
@@ -2847,12 +2848,12 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M36" s="3" t="n"/>
@@ -2910,12 +2911,12 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M37" s="3" t="n"/>
@@ -2973,12 +2974,12 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M38" s="3" t="n"/>
@@ -3036,12 +3037,12 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M39" s="3" t="n"/>
@@ -3099,12 +3100,12 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M40" s="3" t="n"/>
@@ -3162,12 +3163,12 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M41" s="3" t="n"/>
@@ -3225,12 +3226,12 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M42" s="3" t="n"/>
@@ -3288,12 +3289,12 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M43" s="3" t="n"/>
@@ -3351,12 +3352,12 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M44" s="3" t="n"/>
@@ -3414,12 +3415,12 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M45" s="3" t="n"/>
@@ -3477,12 +3478,12 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M46" s="3" t="n"/>
@@ -3540,12 +3541,12 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M47" s="3" t="n"/>
@@ -3603,12 +3604,12 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M48" s="3" t="n"/>
@@ -3666,12 +3667,12 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M49" s="3" t="n"/>
@@ -3729,12 +3730,12 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M50" s="3" t="n"/>
@@ -3792,12 +3793,12 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M51" s="3" t="n"/>
@@ -3855,12 +3856,12 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M52" s="3" t="n"/>
@@ -3918,12 +3919,12 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M53" s="3" t="n"/>
@@ -3981,12 +3982,12 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M54" s="3" t="n"/>
@@ -4044,12 +4045,12 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M55" s="3" t="n"/>
@@ -4107,12 +4108,12 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M56" s="3" t="n"/>
@@ -4170,12 +4171,12 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M57" s="3" t="n"/>
@@ -4233,12 +4234,12 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M58" s="3" t="n"/>
@@ -4296,12 +4297,12 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M59" s="3" t="n"/>
@@ -4359,12 +4360,12 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M60" s="3" t="n"/>
@@ -4422,12 +4423,12 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M61" s="3" t="n"/>
@@ -4485,12 +4486,12 @@
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M62" s="3" t="n"/>
@@ -4548,12 +4549,12 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M63" s="3" t="n"/>
@@ -4611,12 +4612,12 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M64" s="3" t="n"/>
@@ -4674,12 +4675,12 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M65" s="3" t="n"/>
@@ -4737,12 +4738,12 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M66" s="3" t="n"/>
@@ -4800,12 +4801,12 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M67" s="3" t="n"/>
@@ -4863,12 +4864,12 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M68" s="3" t="n"/>
@@ -4926,12 +4927,12 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M69" s="3" t="n"/>
@@ -4989,12 +4990,12 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M70" s="3" t="n"/>
@@ -5052,12 +5053,12 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M71" s="3" t="n"/>
@@ -5115,12 +5116,12 @@
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M72" s="3" t="n"/>
@@ -5178,12 +5179,12 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M73" s="3" t="n"/>
@@ -5241,12 +5242,12 @@
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M74" s="3" t="n"/>
@@ -5304,12 +5305,12 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M75" s="3" t="n"/>
@@ -5367,12 +5368,12 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M76" s="3" t="n"/>
@@ -5430,12 +5431,12 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M77" s="3" t="n"/>
@@ -5493,12 +5494,12 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M78" s="3" t="n"/>
@@ -5556,12 +5557,12 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M79" s="3" t="n"/>
@@ -5619,12 +5620,12 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M80" s="3" t="n"/>
@@ -5682,12 +5683,12 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M81" s="3" t="n"/>
@@ -5745,12 +5746,12 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M82" s="3" t="n"/>
@@ -5808,12 +5809,12 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L83" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M83" s="3" t="n"/>
@@ -5871,12 +5872,12 @@
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M84" s="3" t="n"/>
@@ -5934,12 +5935,12 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L85" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M85" s="3" t="n"/>
@@ -5997,12 +5998,12 @@
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M86" s="3" t="n"/>
@@ -6060,12 +6061,12 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L87" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M87" s="3" t="n"/>
@@ -6123,12 +6124,12 @@
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M88" s="3" t="n"/>
@@ -6186,12 +6187,12 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L89" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M89" s="3" t="n"/>
@@ -6249,12 +6250,12 @@
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M90" s="3" t="n"/>
@@ -6312,12 +6313,12 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L91" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M91" s="3" t="n"/>
@@ -6375,12 +6376,12 @@
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M92" s="3" t="n"/>
@@ -6438,12 +6439,12 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L93" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M93" s="3" t="n"/>
@@ -6501,12 +6502,12 @@
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M94" s="3" t="n"/>
@@ -6564,12 +6565,12 @@
       </c>
       <c r="K95" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L95" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M95" s="3" t="n"/>
@@ -6627,12 +6628,12 @@
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M96" s="3" t="n"/>
@@ -6690,12 +6691,12 @@
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L97" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M97" s="3" t="n"/>
@@ -6753,12 +6754,12 @@
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L98" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M98" s="3" t="n"/>
@@ -6816,12 +6817,12 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L99" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M99" s="3" t="n"/>
@@ -6879,12 +6880,12 @@
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M100" s="3" t="n"/>
@@ -6942,12 +6943,12 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L101" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M101" s="3" t="n"/>
@@ -7005,12 +7006,12 @@
       </c>
       <c r="K102" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L102" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M102" s="3" t="n"/>
@@ -7068,12 +7069,12 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>не указан (исходный DOCX)</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="L103" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
       <c r="M103" s="3" t="n"/>
@@ -18591,7 +18592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18619,6 +18620,4494 @@
       <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-001</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-001</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-002</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-002</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-003</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-003</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-004</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-004</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-005</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-005</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-006</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-006</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-007</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-007</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-008</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-008</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-009</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-009</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-010</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-010</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-011</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-011</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-012</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-012</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-013</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-013</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-014</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-014</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-015</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-015</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-016</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-016</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-017</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-017</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-018</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-018</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-019</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-019</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-020</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-020</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-021</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-021</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-022</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-022</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-023</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-023</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-024</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-024</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-025</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-025</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-026</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-026</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-027</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-027</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-028</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-028</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-029</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-029</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-030</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-030</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-031</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-031</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-032</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-032</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-033</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-033</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-034</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-034</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-035</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-035</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-036</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-036</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-037</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-037</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-038</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-038</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-039</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-039</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-040</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-040</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-041</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-041</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-042</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-042</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-043</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-043</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-044</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-044</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-045</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-045</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-046</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-046</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-047</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-047</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-048</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-048</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-049</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-049</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-050</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-050</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-051</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-051</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-052</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-052</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-053</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-053</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-054</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-054</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-055</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-055</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-056</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-056</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-057</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-057</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-058</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-058</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-059</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-059</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-060</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-060</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-061</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-061</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-062</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-062</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-063</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-063</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-064</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-064</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-065</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-065</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-066</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-066</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-067</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-067</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-068</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-068</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-069</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-069</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-070</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-070</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-071</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-071</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-072</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-072</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-073</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-073</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-074</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-074</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-075</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-075</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-076</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-076</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-077</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-077</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-078</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-078</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-079</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-079</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-080</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-080</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-081</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-081</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-082</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-082</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-083</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-083</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-084</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-084</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-085</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-085</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-086</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-086</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-087</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-087</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-088</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-088</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-089</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-089</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-090</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-090</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-091</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-091</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-092</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-092</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-093</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-093</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-094</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-094</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-095</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-095</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-096</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-096</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-097</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-097</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-098</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-098</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D197" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-099</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C198" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D198" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-099</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D199" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-100</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-100</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-101</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-101</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-102</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>РОП / Руководитель отдела продаж</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-102</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>Менеджеры продаж</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>Первый пул для отдела продаж</t>
         </is>
       </c>
     </row>
@@ -18642,7 +23131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18656,6 +23145,7 @@
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18671,7 +23161,7 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>Официальная должность</t>
+          <t>Официальные должности</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
@@ -18701,15 +23191,20 @@
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>Срок результата, месяцев</t>
+          <t>Период попыток</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
+          <t>Срок действия результата</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
           <t>Статус</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Версия</t>
         </is>
@@ -18723,12 +23218,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Комплексное тестирование сотрудников Star Building</t>
+          <t>Комплексное тестирование отдела продаж Star Building</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж; Менеджеры продаж</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -18736,26 +23231,37 @@
           <t>Все темы пула 001</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>102</v>
-      </c>
+      <c r="E2" s="3" t="n"/>
       <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
+      <c r="G2" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>1 месяц</t>
+        </is>
+      </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
+          <t>по запросу РОПа</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
           <t>Черновик</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:L2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -19376,7 +23882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -19471,191 +23977,239 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж; Менеджеры продаж</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Проверяющий</t>
+          <t>Автор и проверяющий</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>РОП / Руководитель отдела продаж</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Прямо подтверждены утвержденными регламентами</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>2</v>
+          <t>Порог прохождения</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Частично подтверждены утвержденными регламентами</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>1</v>
+          <t>Доступность попытки</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>1 попытка в месяц</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Требуют предоставления или проверки источника</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>99</v>
+          <t>Срок действия результата</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>по запросу РОПа</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Исправлены явные языковые опечатки</t>
+          <t>Хранение источников</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>ВОП-ПУЛ001-007, ВОП-ПУЛ001-096</t>
+          <t>впоследствии в базе данных</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Сложность: Базовый</t>
+          <t>Прямо подтверждены утвержденными регламентами</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Сложность: Повышенный</t>
+          <t>Частично подтверждены утвержденными регламентами</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Сложность: Средний</t>
+          <t>Требуют предоставления или проверки источника</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>34</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Тема: Договорные модели и лицензирование</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>3</v>
+          <t>Исправлены явные языковые опечатки</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>ВОП-ПУЛ001-007, ВОП-ПУЛ001-096</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Тема: Изыскания, приемка и кадастр</t>
+          <t>Сложность: Базовый</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Тема: Кадровая дисциплина</t>
+          <t>Сложность: Повышенный</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Тема: Коммерческая тайна и безопасность</t>
+          <t>Сложность: Средний</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Тема: Компания: история, миссия и культура</t>
+          <t>Тема: Договорные модели и лицензирование</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Тема: Маркетинг и содержание публикаций</t>
+          <t>Тема: Изыскания, приемка и кадастр</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Тема: Продажи, CRM и переговоры</t>
+          <t>Тема: Кадровая дисциплина</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Тема: Проектирование и экспертиза в РК</t>
+          <t>Тема: Коммерческая тайна и безопасность</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Тема: Склады, автосервисы и логистика</t>
+          <t>Тема: Компания: история, миссия и культура</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
+          <t>Тема: Маркетинг и содержание публикаций</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Тема: Продажи, CRM и переговоры</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Тема: Проектирование и экспертиза в РК</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Тема: Склады, автосервисы и логистика</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
           <t>Тема: Технологии ЛСТК, ТСП и промышленные здания</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n">
+      <c r="B30" s="3" t="n">
         <v>43</v>
       </c>
     </row>
